--- a/data/financial_data_validation_and_analysis.xlsx
+++ b/data/financial_data_validation_and_analysis.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Evi\Desktop\Financial &amp; Tax Impact Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Evi\Desktop\financial-data-validation-and-performance-analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23280" windowHeight="12600" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23280" windowHeight="12600"/>
   </bookViews>
   <sheets>
     <sheet name="Raw Data" sheetId="1" r:id="rId1"/>
@@ -567,7 +567,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -589,6 +589,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -945,7 +951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1114,6 +1120,9 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1132,10 +1141,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6413,91 +6422,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1006402</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>43462</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>99906</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1006402" y="10132342"/>
-          <a:ext cx="11718998" cy="605084"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-        <a:effectLst>
-          <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="40000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>Revenue growth varies across companies, with tech firms such as NVDA and AMZN showing stronger and more volatile growth compared</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1">
-              <a:latin typeface="+mn-lt"/>
-            </a:rPr>
-            <a:t>to more stable players like AAPL and MSFT.</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>228723</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -7203,34 +7127,35 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -7239,19 +7164,19 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="58" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="58" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="58" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -7281,7 +7206,7 @@
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="58" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -28754,14 +28679,14 @@
       <c r="B9" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="60"/>
+      <c r="H9" s="61"/>
     </row>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="45" t="s">
@@ -29167,14 +29092,14 @@
       <c r="B8" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
+      <c r="H8" s="61"/>
     </row>
     <row r="9" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="48" t="s">
@@ -29579,14 +29504,14 @@
       <c r="B9" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="63"/>
     </row>
     <row r="10" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="45" t="s">
@@ -29989,293 +29914,293 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="63"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="3" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
     </row>
     <row r="5" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
     </row>
     <row r="6" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="63"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="63"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="63"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="63"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
     </row>
     <row r="14" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="63"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="63"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
     </row>
     <row r="17" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="64"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="63"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="A18" s="64"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
     </row>
     <row r="19" spans="1:5" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
     </row>
     <row r="20" spans="1:5" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="63"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="63"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="63" t="s">
+      <c r="A23" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="63" t="s">
+      <c r="A25" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
     </row>
     <row r="26" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="63"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="63" t="s">
+      <c r="A27" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="63"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="64"/>
+      <c r="C28" s="64"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
     </row>
     <row r="30" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="63"/>
-      <c r="B30" s="63"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
+      <c r="A30" s="64"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
     </row>
     <row r="31" spans="1:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
     </row>
     <row r="32" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="63"/>
-      <c r="B32" s="63"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
     </row>
     <row r="33" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="63"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="64"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
+      <c r="A34" s="66"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="64"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
+      <c r="A35" s="66"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -30284,11 +30209,6 @@
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
@@ -30296,11 +30216,11 @@
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A8:E8"/>
@@ -30308,12 +30228,17 @@
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
